--- a/outputs/53449.xlsx
+++ b/outputs/53449.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
   <si>
     <t xml:space="preserve">Svc_Date</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t xml:space="preserve">Covid Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X</t>
   </si>
   <si>
     <t xml:space="preserve">Aurora</t>
@@ -282,55 +285,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -586,34 +589,34 @@
   <dimension ref="A1:G16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -636,10 +639,6 @@
       <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="0" t="str">
-        <f aca="false">IF(F2="Covid Test","X","")</f>
-        <v/>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="n">
@@ -660,10 +659,6 @@
       <c r="F3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="0" t="str">
-        <f aca="false">IF(F3="Covid Test","X","")</f>
-        <v/>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="n">
@@ -684,10 +679,6 @@
       <c r="F4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="0" t="str">
-        <f aca="false">IF(F4="Covid Test","X","")</f>
-        <v/>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
@@ -708,10 +699,6 @@
       <c r="F5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="0" t="str">
-        <f aca="false">IF(F5="Covid Test","X","")</f>
-        <v/>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
@@ -732,10 +719,6 @@
       <c r="F6" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="0" t="str">
-        <f aca="false">IF(F6="Covid Test","X","")</f>
-        <v/>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
@@ -756,9 +739,8 @@
       <c r="F7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G7" s="0" t="str">
-        <f aca="false">IF(F7="Covid Test","X","")</f>
-        <v>X</v>
+      <c r="G7" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -766,23 +748,22 @@
         <v>44289</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>5545</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="0" t="str">
-        <f aca="false">IF(F8="Covid Test","X","")</f>
-        <v>X</v>
+      <c r="G8" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -790,23 +771,19 @@
         <v>44289</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>5545</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="G9" s="0" t="str">
-        <f aca="false">IF(F9="Covid Test","X","")</f>
-        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -814,23 +791,19 @@
         <v>44289</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>5545</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="G10" s="0" t="str">
-        <f aca="false">IF(F10="Covid Test","X","")</f>
-        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -838,7 +811,7 @@
         <v>44290</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>2234</v>
@@ -851,10 +824,6 @@
       </c>
       <c r="F11" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="G11" s="0" t="str">
-        <f aca="false">IF(F11="Covid Test","X","")</f>
-        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -862,7 +831,7 @@
         <v>44290</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>2234</v>
@@ -871,14 +840,10 @@
         <v>14</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>16</v>
-      </c>
-      <c r="G12" s="0" t="str">
-        <f aca="false">IF(F12="Covid Test","X","")</f>
-        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -886,7 +851,7 @@
         <v>44290</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>2234</v>
@@ -895,14 +860,10 @@
         <v>14</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="G13" s="0" t="str">
-        <f aca="false">IF(F13="Covid Test","X","")</f>
-        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -919,14 +880,10 @@
         <v>8</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="0" t="str">
-        <f aca="false">IF(F14="Covid Test","X","")</f>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -943,14 +900,10 @@
         <v>8</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="G15" s="0" t="str">
-        <f aca="false">IF(F15="Covid Test","X","")</f>
-        <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -967,14 +920,10 @@
         <v>14</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="0" t="str">
-        <f aca="false">IF(F16="Covid Test","X","")</f>
-        <v/>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/53449.xlsx
+++ b/outputs/53449.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
   <si>
     <t xml:space="preserve">Svc_Date</t>
   </si>
@@ -40,9 +40,6 @@
     <t xml:space="preserve">Procedure Category ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Test</t>
-  </si>
-  <si>
     <t xml:space="preserve">Denver</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">Covid Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X</t>
   </si>
   <si>
     <t xml:space="preserve">Aurora</t>
@@ -616,28 +610,29 @@
       <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="n">
         <v>1234</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>10</v>
+      <c r="G2" s="1" t="str">
+        <f aca="false">IF(F2="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -645,19 +640,23 @@
         <v>44287</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="9" t="n">
         <v>1234</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="str">
+        <f aca="false">IF(F3="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -665,19 +664,23 @@
         <v>44287</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>1234</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="G4" s="1" t="str">
+        <f aca="false">IF(F4="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -685,19 +688,23 @@
         <v>44288</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>2234</v>
       </c>
       <c r="D5" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>16</v>
+      <c r="G5" s="1" t="str">
+        <f aca="false">IF(F5="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -705,19 +712,23 @@
         <v>44288</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>2234</v>
       </c>
       <c r="D6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>16</v>
+      <c r="G6" s="1" t="str">
+        <f aca="false">IF(F6="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -725,22 +736,23 @@
         <v>44288</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>2234</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>19</v>
+      <c r="G7" s="1" t="str">
+        <f aca="false">IF(F7="Covid Test","X","")</f>
+        <v>X</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -748,22 +760,23 @@
         <v>44289</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>5545</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="str">
+        <f aca="false">IF(F8="Covid Test","X","")</f>
+        <v>X</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -771,19 +784,23 @@
         <v>44289</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>5545</v>
       </c>
       <c r="D9" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="F9" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G9" s="1" t="str">
+        <f aca="false">IF(F9="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -791,19 +808,23 @@
         <v>44289</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>5545</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G10" s="1" t="str">
+        <f aca="false">IF(F10="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -811,19 +832,23 @@
         <v>44290</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>2234</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="10" t="s">
-        <v>16</v>
+      <c r="G11" s="1" t="str">
+        <f aca="false">IF(F11="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -831,19 +856,23 @@
         <v>44290</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>2234</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G12" s="1" t="str">
+        <f aca="false">IF(F12="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -851,19 +880,23 @@
         <v>44290</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>2234</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G13" s="1" t="str">
+        <f aca="false">IF(F13="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -871,19 +904,23 @@
         <v>44290</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>5545</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="G14" s="1" t="str">
+        <f aca="false">IF(F14="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -891,19 +928,23 @@
         <v>44290</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>5545</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G15" s="1" t="str">
+        <f aca="false">IF(F15="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -911,19 +952,23 @@
         <v>44291</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="12" t="n">
         <v>1234</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
+      </c>
+      <c r="G16" s="1" t="str">
+        <f aca="false">IF(F16="Covid Test","X","")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
